--- a/Scalable_Work/Complete Extraction Results.xlsx
+++ b/Scalable_Work/Complete Extraction Results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kasif\Documents\Qatar-Environment-and-Energy-Research-Institute-Internship-Work-\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kasif\Documents\Qatar-Environment-and-Energy-Research-Institute-Internship-Work-\Scalable_Work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC3C17E2-2297-490C-B6D5-EC8C3F58BF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ABF7C75-86C6-4663-BD0A-9AE9616C4DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{D029F850-DD1B-4CC2-9730-F8119DD79F26}"/>
   </bookViews>
@@ -1826,7 +1826,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2021,6 +2021,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7773,7 +7776,7 @@
     </row>
     <row r="29" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A29" s="11"/>
-      <c r="B29" s="73" t="s">
+      <c r="B29" s="75" t="s">
         <v>111</v>
       </c>
       <c r="C29" s="4" t="s">
@@ -30370,7 +30373,7 @@
       </c>
     </row>
     <row r="239" spans="2:65" x14ac:dyDescent="0.3">
-      <c r="B239" s="11" t="s">
+      <c r="B239" s="73" t="s">
         <v>168</v>
       </c>
       <c r="C239" s="4" t="s">
